--- a/docs/网址工具等/excel/dummy.xlsx
+++ b/docs/网址工具等/excel/dummy.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="270">
   <si>
     <t>库</t>
   </si>
@@ -835,6 +835,9 @@
   </si>
   <si>
     <t>LQFP-48(7x7)</t>
+  </si>
+  <si>
+    <t>[[https://djlv.github.io/node-v/docs/%E7%AC%94%E8%AE%B0/home.html]]</t>
   </si>
 </sst>
 </file>
@@ -4681,10 +4684,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultColWidth="8.79279279279279" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="43.3963963963964" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:23">
       <c r="A1">
         <v>1</v>
       </c>
@@ -4739,10 +4745,25 @@
       <c r="R1">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2">
-        <v>100</v>
+      <c r="S1">
+        <v>19</v>
+      </c>
+      <c r="T1">
+        <v>20</v>
+      </c>
+      <c r="U1">
+        <v>21</v>
+      </c>
+      <c r="V1">
+        <v>22</v>
+      </c>
+      <c r="W1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" t="s">
+        <v>269</v>
       </c>
       <c r="B2">
         <v>101</v>
@@ -4792,11 +4813,8 @@
       <c r="Q2">
         <v>116</v>
       </c>
-      <c r="R2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>101</v>
       </c>
@@ -4852,7 +4870,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>102</v>
       </c>
@@ -4908,7 +4926,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>103</v>
       </c>
@@ -4964,7 +4982,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>104</v>
       </c>
@@ -5020,7 +5038,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>105</v>
       </c>
@@ -5076,7 +5094,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>106</v>
       </c>
@@ -5132,7 +5150,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>107</v>
       </c>
@@ -5188,7 +5206,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>108</v>
       </c>
@@ -5244,7 +5262,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>109</v>
       </c>
@@ -5300,7 +5318,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>110</v>
       </c>
@@ -5356,7 +5374,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>111</v>
       </c>
@@ -5412,7 +5430,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>112</v>
       </c>
@@ -5468,7 +5486,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>113</v>
       </c>
@@ -5524,7 +5542,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>114</v>
       </c>
